--- a/example/Logistics/logistics_status.xlsx
+++ b/example/Logistics/logistics_status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allen.hong\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\ECgithub\SDK_PHP\example\Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF6ED811-73CB-444F-9C8E-4A163ACE722E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FF5EB2-1589-46EC-9BE0-CAACD881AA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統一超商(Unimart)" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="236">
   <si>
     <t>物流類型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -823,6 +823,18 @@
   </si>
   <si>
     <t>包裹重新配達寄件門市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包裹門市確認中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包裹確認中，將退回物流中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>門市誤刷取件，包裹退回中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1355,10 +1367,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3285,7 +3297,7 @@
         <v>2053</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>66</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3327,7 +3339,7 @@
         <v>2062</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>69</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3341,7 +3353,7 @@
         <v>2066</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>69</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -5994,7 +6006,7 @@
         <v>2053</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>66</v>
+        <v>235</v>
       </c>
       <c r="I60" s="1"/>
     </row>
@@ -6114,7 +6126,7 @@
         <v>2062</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>69</v>
+        <v>233</v>
       </c>
       <c r="I68" s="1"/>
     </row>
@@ -6159,7 +6171,7 @@
         <v>2066</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>69</v>
+        <v>234</v>
       </c>
       <c r="I71" s="1"/>
     </row>
@@ -10377,7 +10389,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="70"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
@@ -10392,7 +10404,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A4" s="69"/>
+      <c r="A4" s="70"/>
       <c r="B4" s="55" t="s">
         <v>3</v>
       </c>

--- a/example/Logistics/logistics_status.xlsx
+++ b/example/Logistics/logistics_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\ECgithub\SDK_PHP\example\Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FF5EB2-1589-46EC-9BE0-CAACD881AA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1FC427-9CA6-474C-8F1F-CF4BE3473D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統一超商(Unimart)" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="242">
   <si>
     <t>物流類型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -347,10 +347,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>賣家未取包裹，宅配退回中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>退貨便收件(商品退回指定C門市)</t>
   </si>
   <si>
@@ -835,6 +831,39 @@
   </si>
   <si>
     <t>門市誤刷取件，包裹退回中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包裹宅配退回中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新貨態說明:門市誤刷取件，包裹退回中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新貨態說明:包裹確認中，將退回物流中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新貨態說明:包裹門市確認中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新貨態說明:包裹宅配退回中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIMARTC2C
+HILIFE
+HILIFEC2C
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIMARTC2C
+HILIFE
+HILIFEC2C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1159,7 +1188,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1372,6 +1401,18 @@
     </xf>
     <xf numFmtId="14" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1926,13 +1967,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C1"/>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C2"/>
     </row>
@@ -1947,7 +1988,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="17" customFormat="1" ht="17.25" thickBot="1">
@@ -1981,7 +2022,7 @@
         <v>310</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2289,7 +2330,7 @@
         <v>2021</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2485,7 +2526,7 @@
         <v>2035</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2975,7 +3016,7 @@
         <v>2072</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3031,7 +3072,7 @@
         <v>2095</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3045,7 +3086,7 @@
         <v>2098</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3297,7 +3338,7 @@
         <v>2053</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3311,7 +3352,7 @@
         <v>2058</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3339,7 +3380,7 @@
         <v>2062</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3353,7 +3394,7 @@
         <v>2066</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3436,7 @@
         <v>2069</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3423,7 +3464,7 @@
         <v>2072</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3563,7 +3604,7 @@
         <v>2082</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3577,7 +3618,7 @@
         <v>2083</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3731,7 +3772,7 @@
         <v>2097</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>91</v>
+        <v>235</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3745,7 +3786,7 @@
         <v>2098</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3759,7 +3800,7 @@
         <v>2099</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3773,7 +3814,7 @@
         <v>2101</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3787,7 +3828,7 @@
         <v>2102</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3801,7 +3842,7 @@
         <v>2103</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3885,7 +3926,7 @@
         <v>7019</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3968,7 @@
         <v>9999</v>
       </c>
       <c r="D145" s="36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4049,12 +4090,12 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4068,7 +4109,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.25" thickBot="1">
@@ -4102,7 +4143,7 @@
         <v>310</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4144,7 +4185,7 @@
         <v>3019</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4214,7 +4255,7 @@
         <v>3024</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4242,7 +4283,7 @@
         <v>3029</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4256,7 +4297,7 @@
         <v>3031</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4270,7 +4311,7 @@
         <v>3032</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4298,7 +4339,7 @@
         <v>4002</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4354,7 +4395,7 @@
         <v>7008</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4410,7 +4451,7 @@
         <v>7012</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4452,7 +4493,7 @@
         <v>7015</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -4480,7 +4521,7 @@
         <v>7032</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -4494,7 +4535,7 @@
         <v>7033</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -4508,7 +4549,7 @@
         <v>7034</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -4522,7 +4563,7 @@
         <v>7035</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -4536,7 +4577,7 @@
         <v>7036</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="17.25" thickBot="1">
@@ -4550,7 +4591,7 @@
         <v>7037</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -4578,7 +4619,7 @@
         <v>310</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -4620,7 +4661,7 @@
         <v>3019</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -4690,7 +4731,7 @@
         <v>3024</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -4718,7 +4759,7 @@
         <v>3029</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -4732,7 +4773,7 @@
         <v>3031</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -4746,7 +4787,7 @@
         <v>3032</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -4830,7 +4871,7 @@
         <v>7008</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -4886,7 +4927,7 @@
         <v>7012</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -4928,7 +4969,7 @@
         <v>7015</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -4956,7 +4997,7 @@
         <v>7032</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -4970,7 +5011,7 @@
         <v>7034</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -4984,7 +5025,7 @@
         <v>7035</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="17.25" thickBot="1">
@@ -4998,7 +5039,7 @@
         <v>7036</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -5069,12 +5110,12 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="17.25" thickBot="1">
       <c r="A2" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -5102,7 +5143,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="29">
         <v>300</v>
@@ -5119,13 +5160,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C6" s="19">
         <v>310</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -5137,13 +5178,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C7" s="19">
         <v>311</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -5152,13 +5193,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="19">
         <v>325</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -5170,7 +5211,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="19">
         <v>2000</v>
@@ -5188,7 +5229,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C10" s="19">
         <v>2001</v>
@@ -5205,7 +5246,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="19">
         <v>2002</v>
@@ -5223,13 +5264,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C12" s="19">
         <v>2003</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -5241,13 +5282,13 @@
         <v>3</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="19">
         <v>2004</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -5259,13 +5300,13 @@
         <v>3</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C14" s="19">
         <v>2005</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -5277,7 +5318,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" s="19">
         <v>2006</v>
@@ -5295,7 +5336,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" s="19">
         <v>2007</v>
@@ -5313,7 +5354,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" s="19">
         <v>2009</v>
@@ -5331,7 +5372,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="19">
         <v>2010</v>
@@ -5349,7 +5390,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="19">
         <v>2011</v>
@@ -5365,7 +5406,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="19">
         <v>2012</v>
@@ -5381,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" s="19">
         <v>2013</v>
@@ -5398,7 +5439,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="19">
         <v>2014</v>
@@ -5415,7 +5456,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="19">
         <v>2015</v>
@@ -5432,7 +5473,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" s="19">
         <v>2016</v>
@@ -5449,7 +5490,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="19">
         <v>2017</v>
@@ -5466,7 +5507,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C26" s="19">
         <v>2018</v>
@@ -5483,7 +5524,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C27" s="19">
         <v>2019</v>
@@ -5500,7 +5541,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C28" s="19">
         <v>2020</v>
@@ -5517,7 +5558,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C29" s="19">
         <v>2021</v>
@@ -5534,7 +5575,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C30" s="19">
         <v>2022</v>
@@ -5551,7 +5592,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C31" s="19">
         <v>2023</v>
@@ -5568,7 +5609,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C32" s="19">
         <v>2024</v>
@@ -5585,7 +5626,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C33" s="19">
         <v>2025</v>
@@ -5602,7 +5643,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C34" s="19">
         <v>2026</v>
@@ -5619,7 +5660,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C35" s="19">
         <v>2027</v>
@@ -5636,7 +5677,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C36" s="19">
         <v>2028</v>
@@ -5653,7 +5694,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C37" s="19">
         <v>2029</v>
@@ -5670,7 +5711,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C38" s="19">
         <v>2030</v>
@@ -5685,7 +5726,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C39" s="19">
         <v>2031</v>
@@ -5700,7 +5741,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C40" s="19">
         <v>2032</v>
@@ -5715,7 +5756,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C41" s="19">
         <v>2033</v>
@@ -5730,7 +5771,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C42" s="19">
         <v>2034</v>
@@ -5745,7 +5786,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C43" s="19">
         <v>2035</v>
@@ -5760,7 +5801,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="19">
         <v>2036</v>
@@ -5775,7 +5816,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C45" s="19">
         <v>2037</v>
@@ -5790,7 +5831,7 @@
         <v>3</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C46" s="19">
         <v>2038</v>
@@ -5805,7 +5846,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C47" s="19">
         <v>2039</v>
@@ -5820,7 +5861,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C48" s="19">
         <v>2040</v>
@@ -5835,7 +5876,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C49" s="19">
         <v>2041</v>
@@ -5850,7 +5891,7 @@
         <v>3</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C50" s="19">
         <v>2042</v>
@@ -5865,7 +5906,7 @@
         <v>3</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C51" s="19">
         <v>2043</v>
@@ -5880,7 +5921,7 @@
         <v>3</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C52" s="19">
         <v>2045</v>
@@ -5895,7 +5936,7 @@
         <v>3</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C53" s="19">
         <v>2046</v>
@@ -5910,7 +5951,7 @@
         <v>3</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C54" s="19">
         <v>2047</v>
@@ -5925,7 +5966,7 @@
         <v>3</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C55" s="19">
         <v>2048</v>
@@ -5940,7 +5981,7 @@
         <v>3</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C56" s="19">
         <v>2049</v>
@@ -5955,7 +5996,7 @@
         <v>3</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C57" s="19">
         <v>2050</v>
@@ -5970,7 +6011,7 @@
         <v>3</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="19">
         <v>2051</v>
@@ -5985,7 +6026,7 @@
         <v>3</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C59" s="19">
         <v>2052</v>
@@ -6000,13 +6041,13 @@
         <v>3</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C60" s="19">
         <v>2053</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I60" s="1"/>
     </row>
@@ -6015,7 +6056,7 @@
         <v>3</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C61" s="19">
         <v>2054</v>
@@ -6030,7 +6071,7 @@
         <v>3</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C62" s="19">
         <v>2055</v>
@@ -6045,7 +6086,7 @@
         <v>3</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C63" s="19">
         <v>2057</v>
@@ -6060,7 +6101,7 @@
         <v>3</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C64" s="19">
         <v>2058</v>
@@ -6075,7 +6116,7 @@
         <v>3</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C65" s="19">
         <v>2059</v>
@@ -6090,7 +6131,7 @@
         <v>3</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C66" s="19">
         <v>2060</v>
@@ -6105,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C67" s="19">
         <v>2061</v>
@@ -6120,13 +6161,13 @@
         <v>3</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C68" s="19">
         <v>2062</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I68" s="1"/>
     </row>
@@ -6135,7 +6176,7 @@
         <v>3</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C69" s="19">
         <v>2063</v>
@@ -6150,7 +6191,7 @@
         <v>3</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C70" s="19">
         <v>2065</v>
@@ -6165,13 +6206,13 @@
         <v>3</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C71" s="19">
         <v>2066</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I71" s="1"/>
     </row>
@@ -6180,7 +6221,7 @@
         <v>3</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C72" s="19">
         <v>2067</v>
@@ -6195,7 +6236,7 @@
         <v>3</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C73" s="19">
         <v>2068</v>
@@ -6210,13 +6251,13 @@
         <v>3</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C74" s="19">
         <v>2069</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I74" s="1"/>
     </row>
@@ -6225,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C75" s="19">
         <v>2070</v>
@@ -6240,7 +6281,7 @@
         <v>3</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C76" s="19">
         <v>2071</v>
@@ -6255,13 +6296,13 @@
         <v>3</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C77" s="19">
         <v>2072</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I77" s="1"/>
     </row>
@@ -6270,7 +6311,7 @@
         <v>3</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C78" s="19">
         <v>2073</v>
@@ -6285,7 +6326,7 @@
         <v>3</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C79" s="19">
         <v>2074</v>
@@ -6300,13 +6341,13 @@
         <v>3</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C80" s="19">
         <v>2075</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I80" s="1"/>
     </row>
@@ -6315,13 +6356,13 @@
         <v>3</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" s="19">
         <v>2101</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I81" s="1"/>
     </row>
@@ -6330,13 +6371,13 @@
         <v>3</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C82" s="19">
         <v>2102</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I82" s="1"/>
     </row>
@@ -6345,13 +6386,13 @@
         <v>3</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C83" s="19">
         <v>2103</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I83" s="1"/>
     </row>
@@ -6360,7 +6401,7 @@
         <v>3</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C84" s="19">
         <v>2104</v>
@@ -6376,7 +6417,7 @@
         <v>3</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C85" s="19">
         <v>2105</v>
@@ -6392,7 +6433,7 @@
         <v>3</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C86" s="19">
         <v>3018</v>
@@ -6409,13 +6450,13 @@
         <v>3</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C87" s="19">
         <v>3019</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I87" s="1"/>
       <c r="K87" s="1"/>
@@ -6425,7 +6466,7 @@
         <v>3</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C88" s="19">
         <v>3020</v>
@@ -6442,7 +6483,7 @@
         <v>3</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C89" s="19">
         <v>3021</v>
@@ -6457,7 +6498,7 @@
         <v>3</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C90" s="19">
         <v>3022</v>
@@ -6474,7 +6515,7 @@
         <v>3</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C91" s="19">
         <v>3023</v>
@@ -6491,13 +6532,13 @@
         <v>3</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C92" s="19">
         <v>3024</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
@@ -6508,7 +6549,7 @@
         <v>3</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C93" s="19">
         <v>3025</v>
@@ -6524,13 +6565,13 @@
         <v>3</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C94" s="19">
         <v>3029</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I94" s="1"/>
     </row>
@@ -6539,13 +6580,13 @@
         <v>3</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C95" s="19">
         <v>3031</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I95" s="1"/>
     </row>
@@ -6554,13 +6595,13 @@
         <v>3</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C96" s="19">
         <v>3032</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I96" s="1"/>
       <c r="K96" s="1"/>
@@ -6570,13 +6611,13 @@
         <v>3</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C97" s="19">
         <v>3033</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I97" s="1"/>
       <c r="K97" s="1"/>
@@ -6586,13 +6627,13 @@
         <v>3</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C98" s="19">
         <v>4001</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I98" s="1"/>
     </row>
@@ -6601,7 +6642,7 @@
         <v>3</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C99" s="19">
         <v>4002</v>
@@ -6616,13 +6657,13 @@
         <v>3</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C100" s="19">
         <v>5001</v>
       </c>
       <c r="D100" s="37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I100" s="1"/>
     </row>
@@ -6631,13 +6672,13 @@
         <v>3</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C101" s="19">
         <v>5002</v>
       </c>
       <c r="D101" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I101" s="1"/>
     </row>
@@ -6646,13 +6687,13 @@
         <v>3</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C102" s="19">
         <v>5003</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I102" s="1"/>
     </row>
@@ -6661,7 +6702,7 @@
         <v>3</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C103" s="19">
         <v>5004</v>
@@ -6677,13 +6718,13 @@
         <v>3</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C104" s="19">
         <v>5005</v>
       </c>
       <c r="D104" s="37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I104" s="1"/>
     </row>
@@ -6692,13 +6733,13 @@
         <v>3</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C105" s="19">
         <v>5006</v>
       </c>
       <c r="D105" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I105" s="1"/>
     </row>
@@ -6707,13 +6748,13 @@
         <v>3</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C106" s="19">
         <v>5007</v>
       </c>
       <c r="D106" s="37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I106" s="1"/>
     </row>
@@ -6722,13 +6763,13 @@
         <v>3</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C107" s="19">
         <v>5008</v>
       </c>
       <c r="D107" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I107" s="1"/>
     </row>
@@ -6737,7 +6778,7 @@
         <v>3</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C108" s="19">
         <v>5009</v>
@@ -6752,13 +6793,13 @@
         <v>3</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C109" s="19">
         <v>7001</v>
       </c>
       <c r="D109" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I109" s="1"/>
     </row>
@@ -6767,13 +6808,13 @@
         <v>3</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C110" s="19">
         <v>7002</v>
       </c>
       <c r="D110" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I110" s="1"/>
     </row>
@@ -6782,13 +6823,13 @@
         <v>3</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C111" s="19">
         <v>7003</v>
       </c>
       <c r="D111" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I111" s="1"/>
     </row>
@@ -6797,13 +6838,13 @@
         <v>3</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C112" s="19">
         <v>7004</v>
       </c>
       <c r="D112" s="37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I112" s="1"/>
     </row>
@@ -6812,13 +6853,13 @@
         <v>3</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C113" s="19">
         <v>7005</v>
       </c>
       <c r="D113" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I113" s="1"/>
     </row>
@@ -6827,7 +6868,7 @@
         <v>3</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C114" s="19">
         <v>7006</v>
@@ -6842,7 +6883,7 @@
         <v>3</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C115" s="19">
         <v>7007</v>
@@ -6857,13 +6898,13 @@
         <v>3</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C116" s="19">
         <v>7008</v>
       </c>
       <c r="D116" s="32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I116" s="1"/>
     </row>
@@ -6872,7 +6913,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C117" s="19">
         <v>7009</v>
@@ -6887,7 +6928,7 @@
         <v>3</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C118" s="19">
         <v>7010</v>
@@ -6902,7 +6943,7 @@
         <v>3</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C119" s="19">
         <v>7011</v>
@@ -6917,13 +6958,13 @@
         <v>3</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C120" s="19">
         <v>7012</v>
       </c>
       <c r="D120" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I120" s="1"/>
     </row>
@@ -6932,7 +6973,7 @@
         <v>3</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C121" s="19">
         <v>7013</v>
@@ -6947,13 +6988,13 @@
         <v>3</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C122" s="19">
         <v>7014</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I122" s="1"/>
     </row>
@@ -6962,7 +7003,7 @@
         <v>3</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C123" s="19">
         <v>7016</v>
@@ -6977,13 +7018,13 @@
         <v>3</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C124" s="19">
         <v>7032</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I124" s="1"/>
     </row>
@@ -6992,13 +7033,13 @@
         <v>3</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C125" s="19">
         <v>9001</v>
       </c>
       <c r="D125" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I125" s="1"/>
     </row>
@@ -7007,13 +7048,13 @@
         <v>3</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C126" s="19">
         <v>9002</v>
       </c>
       <c r="D126" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I126" s="1"/>
     </row>
@@ -7022,13 +7063,13 @@
         <v>3</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C127" s="31">
         <v>9999</v>
       </c>
       <c r="D127" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I127" s="1"/>
     </row>
@@ -7037,7 +7078,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C128" s="43">
         <v>300</v>
@@ -7051,13 +7092,13 @@
         <v>3</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C129" s="19">
         <v>310</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -7065,13 +7106,13 @@
         <v>3</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C130" s="19">
         <v>311</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -7079,13 +7120,13 @@
         <v>3</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C131" s="19">
         <v>325</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -7093,7 +7134,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C132" s="19">
         <v>2000</v>
@@ -7107,7 +7148,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C133" s="19">
         <v>2001</v>
@@ -7121,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C134" s="19">
         <v>2002</v>
@@ -7135,13 +7176,13 @@
         <v>3</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C135" s="19">
         <v>2003</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -7149,13 +7190,13 @@
         <v>3</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C136" s="19">
         <v>2004</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -7163,13 +7204,13 @@
         <v>3</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C137" s="19">
         <v>2005</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -7177,7 +7218,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C138" s="19">
         <v>2006</v>
@@ -7191,7 +7232,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C139" s="19">
         <v>2007</v>
@@ -7205,7 +7246,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C140" s="19">
         <v>2009</v>
@@ -7219,7 +7260,7 @@
         <v>3</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C141" s="19">
         <v>2010</v>
@@ -7233,7 +7274,7 @@
         <v>3</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C142" s="19">
         <v>2011</v>
@@ -7247,7 +7288,7 @@
         <v>3</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C143" s="19">
         <v>2012</v>
@@ -7261,7 +7302,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C144" s="19">
         <v>2013</v>
@@ -7275,7 +7316,7 @@
         <v>3</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C145" s="19">
         <v>2014</v>
@@ -7289,7 +7330,7 @@
         <v>3</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C146" s="19">
         <v>2015</v>
@@ -7303,7 +7344,7 @@
         <v>3</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C147" s="19">
         <v>2016</v>
@@ -7317,7 +7358,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C148" s="19">
         <v>2017</v>
@@ -7331,7 +7372,7 @@
         <v>3</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C149" s="19">
         <v>2018</v>
@@ -7345,7 +7386,7 @@
         <v>3</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C150" s="19">
         <v>2019</v>
@@ -7359,7 +7400,7 @@
         <v>3</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C151" s="19">
         <v>2020</v>
@@ -7373,13 +7414,13 @@
         <v>3</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C152" s="19">
         <v>2021</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -7387,7 +7428,7 @@
         <v>3</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C153" s="19">
         <v>2022</v>
@@ -7401,7 +7442,7 @@
         <v>3</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C154" s="19">
         <v>2023</v>
@@ -7415,7 +7456,7 @@
         <v>3</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C155" s="19">
         <v>2024</v>
@@ -7429,7 +7470,7 @@
         <v>3</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C156" s="19">
         <v>2025</v>
@@ -7443,7 +7484,7 @@
         <v>3</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C157" s="19">
         <v>2026</v>
@@ -7457,7 +7498,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C158" s="19">
         <v>2027</v>
@@ -7471,7 +7512,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C159" s="19">
         <v>2028</v>
@@ -7485,7 +7526,7 @@
         <v>3</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C160" s="19">
         <v>2029</v>
@@ -7499,7 +7540,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C161" s="19">
         <v>2030</v>
@@ -7513,7 +7554,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C162" s="19">
         <v>2031</v>
@@ -7527,7 +7568,7 @@
         <v>3</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C163" s="19">
         <v>2032</v>
@@ -7541,7 +7582,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C164" s="19">
         <v>2033</v>
@@ -7555,7 +7596,7 @@
         <v>3</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C165" s="19">
         <v>2034</v>
@@ -7569,13 +7610,13 @@
         <v>3</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C166" s="19">
         <v>2035</v>
       </c>
       <c r="D166" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -7583,7 +7624,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C167" s="19">
         <v>2036</v>
@@ -7597,7 +7638,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C168" s="19">
         <v>2037</v>
@@ -7611,7 +7652,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C169" s="19">
         <v>2038</v>
@@ -7625,7 +7666,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C170" s="19">
         <v>2039</v>
@@ -7639,7 +7680,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C171" s="19">
         <v>2040</v>
@@ -7653,7 +7694,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C172" s="19">
         <v>2041</v>
@@ -7667,7 +7708,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C173" s="19">
         <v>2042</v>
@@ -7681,7 +7722,7 @@
         <v>3</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C174" s="19">
         <v>2043</v>
@@ -7695,7 +7736,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C175" s="19">
         <v>2045</v>
@@ -7709,7 +7750,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C176" s="19">
         <v>2046</v>
@@ -7723,7 +7764,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C177" s="19">
         <v>2047</v>
@@ -7737,7 +7778,7 @@
         <v>3</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C178" s="19">
         <v>2048</v>
@@ -7751,7 +7792,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C179" s="19">
         <v>2049</v>
@@ -7765,7 +7806,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C180" s="19">
         <v>2050</v>
@@ -7779,7 +7820,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C181" s="19">
         <v>2051</v>
@@ -7793,7 +7834,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C182" s="19">
         <v>2052</v>
@@ -7807,13 +7848,13 @@
         <v>3</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C183" s="19">
         <v>2053</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>66</v>
+        <v>234</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -7821,7 +7862,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C184" s="19">
         <v>2054</v>
@@ -7835,7 +7876,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C185" s="19">
         <v>2055</v>
@@ -7849,7 +7890,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C186" s="19">
         <v>2057</v>
@@ -7863,7 +7904,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C187" s="19">
         <v>2058</v>
@@ -7877,7 +7918,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C188" s="19">
         <v>2059</v>
@@ -7891,7 +7932,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C189" s="19">
         <v>2060</v>
@@ -7905,7 +7946,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C190" s="19">
         <v>2061</v>
@@ -7919,13 +7960,13 @@
         <v>3</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C191" s="19">
         <v>2062</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -7933,7 +7974,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C192" s="19">
         <v>2063</v>
@@ -7947,7 +7988,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C193" s="19">
         <v>2065</v>
@@ -7961,13 +8002,13 @@
         <v>3</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C194" s="19">
         <v>2066</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>69</v>
+        <v>233</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -7975,7 +8016,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C195" s="19">
         <v>2067</v>
@@ -7989,7 +8030,7 @@
         <v>3</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C196" s="19">
         <v>2068</v>
@@ -8003,13 +8044,13 @@
         <v>3</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C197" s="19">
         <v>2069</v>
       </c>
       <c r="D197" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -8017,7 +8058,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C198" s="19">
         <v>2070</v>
@@ -8031,7 +8072,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C199" s="19">
         <v>2071</v>
@@ -8045,13 +8086,13 @@
         <v>3</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C200" s="19">
         <v>2072</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -8059,7 +8100,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C201" s="19">
         <v>2073</v>
@@ -8073,7 +8114,7 @@
         <v>3</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C202" s="19">
         <v>2074</v>
@@ -8087,13 +8128,13 @@
         <v>3</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C203" s="19">
         <v>2075</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -8101,13 +8142,13 @@
         <v>3</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C204" s="19">
         <v>2101</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -8115,13 +8156,13 @@
         <v>3</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C205" s="19">
         <v>2102</v>
       </c>
       <c r="D205" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -8129,13 +8170,13 @@
         <v>3</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C206" s="19">
         <v>2103</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -8143,7 +8184,7 @@
         <v>3</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C207" s="19">
         <v>2104</v>
@@ -8157,7 +8198,7 @@
         <v>3</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C208" s="19">
         <v>2105</v>
@@ -8171,7 +8212,7 @@
         <v>3</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C209" s="19">
         <v>3018</v>
@@ -8185,13 +8226,13 @@
         <v>3</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C210" s="19">
         <v>3019</v>
       </c>
       <c r="D210" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -8199,7 +8240,7 @@
         <v>3</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C211" s="19">
         <v>3020</v>
@@ -8213,7 +8254,7 @@
         <v>3</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C212" s="19">
         <v>3021</v>
@@ -8227,7 +8268,7 @@
         <v>3</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C213" s="19">
         <v>3022</v>
@@ -8241,7 +8282,7 @@
         <v>3</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C214" s="19">
         <v>3023</v>
@@ -8255,13 +8296,13 @@
         <v>3</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C215" s="19">
         <v>3024</v>
       </c>
       <c r="D215" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -8269,7 +8310,7 @@
         <v>3</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C216" s="19">
         <v>3025</v>
@@ -8283,13 +8324,13 @@
         <v>3</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C217" s="19">
         <v>3029</v>
       </c>
       <c r="D217" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -8297,13 +8338,13 @@
         <v>3</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C218" s="19">
         <v>3031</v>
       </c>
       <c r="D218" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -8311,13 +8352,13 @@
         <v>3</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C219" s="19">
         <v>3032</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -8325,13 +8366,13 @@
         <v>3</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C220" s="19">
         <v>3033</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -8339,13 +8380,13 @@
         <v>3</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C221" s="19">
         <v>4001</v>
       </c>
       <c r="D221" s="32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -8353,7 +8394,7 @@
         <v>3</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C222" s="19">
         <v>4002</v>
@@ -8367,13 +8408,13 @@
         <v>3</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C223" s="19">
         <v>5001</v>
       </c>
       <c r="D223" s="37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -8381,13 +8422,13 @@
         <v>3</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C224" s="19">
         <v>5002</v>
       </c>
       <c r="D224" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -8395,13 +8436,13 @@
         <v>3</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C225" s="19">
         <v>5003</v>
       </c>
       <c r="D225" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -8409,7 +8450,7 @@
         <v>3</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C226" s="19">
         <v>5004</v>
@@ -8423,13 +8464,13 @@
         <v>3</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C227" s="19">
         <v>5005</v>
       </c>
       <c r="D227" s="37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -8437,13 +8478,13 @@
         <v>3</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C228" s="19">
         <v>5006</v>
       </c>
       <c r="D228" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -8451,13 +8492,13 @@
         <v>3</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C229" s="19">
         <v>5007</v>
       </c>
       <c r="D229" s="37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -8465,13 +8506,13 @@
         <v>3</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C230" s="19">
         <v>5008</v>
       </c>
       <c r="D230" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -8479,7 +8520,7 @@
         <v>3</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C231" s="19">
         <v>5009</v>
@@ -8493,13 +8534,13 @@
         <v>3</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C232" s="19">
         <v>7001</v>
       </c>
       <c r="D232" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -8507,13 +8548,13 @@
         <v>3</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C233" s="19">
         <v>7002</v>
       </c>
       <c r="D233" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -8521,13 +8562,13 @@
         <v>3</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C234" s="19">
         <v>7003</v>
       </c>
       <c r="D234" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -8535,13 +8576,13 @@
         <v>3</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C235" s="19">
         <v>7004</v>
       </c>
       <c r="D235" s="37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -8549,13 +8590,13 @@
         <v>3</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C236" s="19">
         <v>7005</v>
       </c>
       <c r="D236" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -8563,7 +8604,7 @@
         <v>3</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C237" s="19">
         <v>7006</v>
@@ -8577,7 +8618,7 @@
         <v>3</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C238" s="19">
         <v>7007</v>
@@ -8591,13 +8632,13 @@
         <v>3</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C239" s="19">
         <v>7008</v>
       </c>
       <c r="D239" s="32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -8605,7 +8646,7 @@
         <v>3</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C240" s="19">
         <v>7009</v>
@@ -8619,7 +8660,7 @@
         <v>3</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C241" s="19">
         <v>7010</v>
@@ -8633,7 +8674,7 @@
         <v>3</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C242" s="19">
         <v>7011</v>
@@ -8647,13 +8688,13 @@
         <v>3</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C243" s="19">
         <v>7012</v>
       </c>
       <c r="D243" s="41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -8661,7 +8702,7 @@
         <v>3</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C244" s="19">
         <v>7013</v>
@@ -8675,13 +8716,13 @@
         <v>3</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C245" s="19">
         <v>7014</v>
       </c>
       <c r="D245" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -8689,7 +8730,7 @@
         <v>3</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C246" s="19">
         <v>7016</v>
@@ -8703,13 +8744,13 @@
         <v>3</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C247" s="19">
         <v>7032</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -8717,13 +8758,13 @@
         <v>3</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C248" s="19">
         <v>9001</v>
       </c>
       <c r="D248" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -8731,13 +8772,13 @@
         <v>3</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C249" s="19">
         <v>9002</v>
       </c>
       <c r="D249" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -8745,13 +8786,13 @@
         <v>3</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C250" s="19">
         <v>9999</v>
       </c>
       <c r="D250" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -8816,13 +8857,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C1"/>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C2"/>
     </row>
@@ -8851,7 +8892,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" s="19">
         <v>300</v>
@@ -8865,7 +8906,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C6" s="19">
         <v>2030</v>
@@ -8879,7 +8920,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="19">
         <v>2055</v>
@@ -8893,13 +8934,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C8" s="19">
         <v>2072</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8907,7 +8948,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" s="19">
         <v>2073</v>
@@ -8921,7 +8962,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C10" s="19">
         <v>2074</v>
@@ -8935,7 +8976,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="19">
         <v>2075</v>
@@ -8949,7 +8990,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="19">
         <v>2078</v>
@@ -8963,7 +9004,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" s="19">
         <v>2105</v>
@@ -8977,7 +9018,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="19">
         <v>3021</v>
@@ -8991,7 +9032,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="19">
         <v>3022</v>
@@ -9005,7 +9046,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="19">
         <v>3023</v>
@@ -9019,13 +9060,13 @@
         <v>3</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C17" s="19">
         <v>3032</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -9033,7 +9074,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="19">
         <v>7101</v>
@@ -9047,13 +9088,13 @@
         <v>3</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="19">
         <v>7102</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -9061,13 +9102,13 @@
         <v>3</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C20" s="19">
         <v>7103</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -9075,13 +9116,13 @@
         <v>3</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C21" s="19">
         <v>7104</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -9089,13 +9130,13 @@
         <v>3</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C22" s="19">
         <v>7105</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -9103,13 +9144,13 @@
         <v>3</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C23" s="19">
         <v>7106</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -9117,13 +9158,13 @@
         <v>3</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C24" s="19">
         <v>7107</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -9131,13 +9172,13 @@
         <v>3</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="19">
         <v>7201</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -9145,13 +9186,13 @@
         <v>3</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" s="19">
         <v>7202</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -9159,13 +9200,13 @@
         <v>3</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27" s="19">
         <v>7203</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -9173,13 +9214,13 @@
         <v>3</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="19">
         <v>7204</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -9187,13 +9228,13 @@
         <v>3</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C29" s="19">
         <v>7205</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -9201,13 +9242,13 @@
         <v>3</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C30" s="19">
         <v>7206</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -9215,13 +9256,13 @@
         <v>3</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C31" s="19">
         <v>7207</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -9229,13 +9270,13 @@
         <v>3</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="19">
         <v>7255</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -9263,13 +9304,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C1"/>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C2"/>
     </row>
@@ -9295,716 +9336,716 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C5" s="19">
         <v>311</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C6" s="19">
         <v>300</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C7" s="19">
         <v>310</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C8" s="19">
         <v>325</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C9" s="19">
         <v>3001</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C10" s="19">
         <v>3002</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C11" s="19">
         <v>3003</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C12" s="19">
         <v>3004</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C13" s="19">
         <v>3005</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C14" s="19">
         <v>3006</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="19">
         <v>3007</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C16" s="19">
         <v>3008</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C17" s="19">
         <v>3009</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C18" s="19">
         <v>3010</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C19" s="19">
         <v>3011</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C20" s="19">
         <v>3012</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C21" s="19">
         <v>3013</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C22" s="19">
         <v>3014</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C23" s="19">
         <v>3015</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C24" s="19">
         <v>3016</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C25" s="19">
         <v>3017</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C26" s="19">
         <v>3117</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C27" s="19">
         <v>3118</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C28" s="19">
         <v>3119</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C29" s="19">
         <v>3120</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C30" s="19">
         <v>3121</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C31" s="19">
         <v>3122</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C32" s="19">
         <v>3123</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C33" s="19">
         <v>3124</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C34" s="19">
         <v>3125</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C35" s="19">
         <v>5001</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C36" s="19">
         <v>5002</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C37" s="19">
         <v>5003</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C38" s="19">
         <v>5004</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C39" s="19">
         <v>5005</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C40" s="19">
         <v>5006</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C41" s="19">
         <v>5007</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C42" s="19">
         <v>5008</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C43" s="19">
         <v>7001</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C44" s="19">
         <v>7002</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C45" s="19">
         <v>7003</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C46" s="19">
         <v>7004</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C47" s="19">
         <v>7005</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C48" s="19">
         <v>7024</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C49" s="19">
         <v>7025</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C50" s="19">
         <v>7026</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C51" s="19">
         <v>7027</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C52" s="19">
         <v>7028</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C53" s="19">
         <v>7029</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C54" s="19">
         <v>7030</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C55" s="19">
         <v>7031</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -10033,13 +10074,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C1"/>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1">
       <c r="A2" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C2"/>
     </row>
@@ -10065,268 +10106,268 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C5" s="19">
         <v>3301</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" s="19">
         <v>3302</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C7" s="19">
         <v>3303</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" s="19">
         <v>3304</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C9" s="19">
         <v>3305</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="19">
         <v>3306</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C11" s="19">
         <v>3307</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C12" s="19">
         <v>3308</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C13" s="19">
         <v>3309</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C14" s="19">
         <v>3310</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C15" s="19">
         <v>3311</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="19">
         <v>3312</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="19">
         <v>3313</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C18" s="19">
         <v>3314</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C19" s="19">
         <v>3315</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C20" s="19">
         <v>7300</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C21" s="19">
         <v>7301</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C22" s="19">
         <v>7302</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C23" s="19">
         <v>320</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -10343,7 +10384,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="21.5" style="56" customWidth="1"/>
@@ -10356,7 +10397,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B1" s="57" t="s">
         <v>0</v>
@@ -10368,178 +10409,180 @@
         <v>2</v>
       </c>
       <c r="E1" s="57" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="66">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63">
+      <c r="A2" s="71">
+        <v>46155</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="58">
+        <v>2053</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="47.25">
+      <c r="A3" s="72"/>
+      <c r="B3" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" s="58">
+        <v>2066</v>
+      </c>
+      <c r="E3" s="58" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="47.25">
+      <c r="A4" s="72"/>
+      <c r="B4" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" s="58">
+        <v>2062</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.5" customHeight="1">
+      <c r="A5" s="73"/>
+      <c r="B5" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="58">
+        <v>2097</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A6" s="66">
         <v>45902</v>
       </c>
-      <c r="B2" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="55" t="s">
+      <c r="B6" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D6" s="58">
         <v>2098</v>
       </c>
-      <c r="E2" s="58" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="55" t="s">
+      <c r="E6" s="58" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A7" s="69"/>
+      <c r="B7" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D7" s="58">
         <v>2098</v>
       </c>
-      <c r="E3" s="58" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="55" t="s">
+      <c r="E7" s="58" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A8" s="70"/>
+      <c r="B8" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D8" s="59">
         <v>2099</v>
       </c>
-      <c r="E4" s="58" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A5" s="66">
+      <c r="E8" s="58" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A9" s="66">
         <v>45839</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B9" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="D9" s="58">
+        <v>3123</v>
+      </c>
+      <c r="E9" s="58" t="s">
         <v>229</v>
       </c>
-      <c r="D5" s="58">
-        <v>3123</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="67"/>
-      <c r="B6" s="58" t="s">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="67"/>
+      <c r="B10" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="D10" s="58">
+        <v>3124</v>
+      </c>
+      <c r="E10" s="58" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="58">
-        <v>3124</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="68"/>
-      <c r="B7" s="58" t="s">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="68"/>
+      <c r="B11" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="D11" s="58">
+        <v>3125</v>
+      </c>
+      <c r="E11" s="58" t="s">
         <v>229</v>
       </c>
-      <c r="D7" s="58">
-        <v>3125</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="64">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="64">
         <v>45652</v>
       </c>
-      <c r="B8" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="55" t="s">
+      <c r="B12" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D12" s="55">
         <v>2021</v>
       </c>
-      <c r="E8" s="55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="65"/>
-      <c r="B9" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="55">
-        <v>2035</v>
-      </c>
-      <c r="E9" s="55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="65"/>
-      <c r="B10" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="55">
-        <v>2082</v>
-      </c>
-      <c r="E10" s="55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="65"/>
-      <c r="B11" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="55">
-        <v>2021</v>
-      </c>
-      <c r="E11" s="55" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="65"/>
-      <c r="B12" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" s="55">
-        <v>2035</v>
-      </c>
       <c r="E12" s="55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -10548,13 +10591,13 @@
         <v>3</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>166</v>
+        <v>6</v>
       </c>
       <c r="D13" s="55">
-        <v>3001</v>
+        <v>2035</v>
       </c>
       <c r="E13" s="55" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -10563,13 +10606,13 @@
         <v>3</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>166</v>
+        <v>7</v>
       </c>
       <c r="D14" s="55">
-        <v>3002</v>
+        <v>2082</v>
       </c>
       <c r="E14" s="55" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -10578,13 +10621,13 @@
         <v>3</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D15" s="55">
-        <v>3003</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="55" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -10593,13 +10636,13 @@
         <v>3</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D16" s="55">
-        <v>3004</v>
+        <v>2035</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -10608,13 +10651,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D17" s="55">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="E17" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -10623,13 +10666,13 @@
         <v>3</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D18" s="55">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="E18" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -10638,13 +10681,13 @@
         <v>3</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D19" s="55">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="E19" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -10653,13 +10696,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D20" s="55">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="E20" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -10668,13 +10711,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D21" s="55">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="E21" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -10683,13 +10726,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D22" s="55">
-        <v>3010</v>
+        <v>3006</v>
       </c>
       <c r="E22" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -10698,13 +10741,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D23" s="55">
-        <v>3011</v>
+        <v>3007</v>
       </c>
       <c r="E23" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -10713,13 +10756,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D24" s="55">
-        <v>3012</v>
+        <v>3008</v>
       </c>
       <c r="E24" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -10728,13 +10771,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D25" s="55">
-        <v>3013</v>
+        <v>3009</v>
       </c>
       <c r="E25" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -10743,13 +10786,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D26" s="55">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="E26" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -10758,13 +10801,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D27" s="55">
-        <v>3015</v>
+        <v>3011</v>
       </c>
       <c r="E27" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -10773,13 +10816,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D28" s="55">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="E28" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -10788,13 +10831,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D29" s="55">
-        <v>3017</v>
+        <v>3013</v>
       </c>
       <c r="E29" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -10803,13 +10846,13 @@
         <v>3</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D30" s="55">
-        <v>2021</v>
+        <v>3014</v>
       </c>
       <c r="E30" s="55" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -10818,13 +10861,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D31" s="55">
-        <v>2035</v>
+        <v>3015</v>
       </c>
       <c r="E31" s="55" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -10833,13 +10876,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D32" s="55">
-        <v>3001</v>
+        <v>3016</v>
       </c>
       <c r="E32" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -10848,13 +10891,13 @@
         <v>3</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D33" s="55">
-        <v>3002</v>
+        <v>3017</v>
       </c>
       <c r="E33" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -10863,13 +10906,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D34" s="55">
-        <v>3003</v>
+        <v>2021</v>
       </c>
       <c r="E34" s="55" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -10878,13 +10921,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D35" s="55">
-        <v>3004</v>
+        <v>2035</v>
       </c>
       <c r="E35" s="55" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -10893,13 +10936,13 @@
         <v>3</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D36" s="55">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="E36" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -10908,13 +10951,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D37" s="55">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="E37" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -10923,13 +10966,13 @@
         <v>3</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D38" s="55">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="E38" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -10938,13 +10981,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D39" s="55">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="E39" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -10953,13 +10996,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D40" s="55">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="E40" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -10968,13 +11011,13 @@
         <v>3</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D41" s="55">
-        <v>3010</v>
+        <v>3006</v>
       </c>
       <c r="E41" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -10983,13 +11026,13 @@
         <v>3</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D42" s="55">
-        <v>3011</v>
+        <v>3007</v>
       </c>
       <c r="E42" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -10998,13 +11041,13 @@
         <v>3</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D43" s="55">
-        <v>3012</v>
+        <v>3008</v>
       </c>
       <c r="E43" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -11013,13 +11056,13 @@
         <v>3</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D44" s="55">
-        <v>3013</v>
+        <v>3009</v>
       </c>
       <c r="E44" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -11028,13 +11071,13 @@
         <v>3</v>
       </c>
       <c r="C45" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D45" s="55">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="E45" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -11043,13 +11086,13 @@
         <v>3</v>
       </c>
       <c r="C46" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D46" s="55">
-        <v>3015</v>
+        <v>3011</v>
       </c>
       <c r="E46" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -11058,13 +11101,13 @@
         <v>3</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D47" s="55">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="E47" s="55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -11073,20 +11116,81 @@
         <v>3</v>
       </c>
       <c r="C48" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D48" s="55">
+        <v>3013</v>
+      </c>
+      <c r="E48" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="65"/>
+      <c r="B49" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" s="55">
+        <v>3014</v>
+      </c>
+      <c r="E49" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="65"/>
+      <c r="B50" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="55">
+        <v>3015</v>
+      </c>
+      <c r="E50" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="65"/>
+      <c r="B51" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="D51" s="55">
+        <v>3016</v>
+      </c>
+      <c r="E51" s="55" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="65"/>
+      <c r="B52" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="55">
         <v>3017</v>
       </c>
-      <c r="E48" s="55" t="s">
-        <v>224</v>
+      <c r="E52" s="55" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:A48"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A2:A4"/>
+  <mergeCells count="4">
+    <mergeCell ref="A12:A52"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A2:A5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
